--- a/Result/profitability/4413.xlsx
+++ b/Result/profitability/4413.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05125</v>
+        <v>0.06375</v>
       </c>
       <c r="N2" t="n">
-        <v>15.2875</v>
+        <v>15.17</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.08</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06375</v>
+        <v>0.05125</v>
       </c>
       <c r="N3" t="n">
-        <v>11.15375</v>
+        <v>11.36875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05249999999999999</v>
+        <v>0.07374999999999998</v>
       </c>
       <c r="N4" t="n">
-        <v>8.725</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03999999999999999</v>
+        <v>0.07875000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.333749999999999</v>
+        <v>-0.2474999999999987</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08875</v>
+        <v>0.03</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.341249999999999</v>
+        <v>-5.138749999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>-0.04</v>
       </c>
       <c r="M7" t="n">
-        <v>0.035</v>
+        <v>-0.07250000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.453749999999999</v>
+        <v>-7.154999999999998</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
         <v>-0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06625</v>
+        <v>-0.095</v>
       </c>
       <c r="N8" t="n">
-        <v>-8.918749999999999</v>
+        <v>-9.354999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1647,7 +1647,7 @@
         <v>-0.05</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07250000000000001</v>
+        <v>-0.0725</v>
       </c>
       <c r="N10" t="n">
         <v>-13.1075</v>
@@ -1776,7 +1776,7 @@
         <v>0.14</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.045</v>
+        <v>-0.04500000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>-11.77125</v>
@@ -2033,7 +2033,7 @@
         <v>0.04375</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.4975</v>
+        <v>-2.497499999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9846,6 +9846,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4413</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>121</v>
+      </c>
+      <c r="D75" t="n">
+        <v>99</v>
+      </c>
+      <c r="E75" t="n">
+        <v>22</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.26%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.41625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.533333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.489999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1595063985374771</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7948717948717949</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.690000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.895876288659794</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
